--- a/DOSSIES_MULTIFORMATO/PMAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/PMAM/dossie.xlsx
@@ -722,7 +722,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023NE0001037</t>
+          <t>2023NE01037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -745,14 +745,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2023 a 02/01/2024. PARECER JURÍDICO Nº 5089/2022</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023NE01037</t>
+          <t>2023NE0001037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2023 a 02/01/2024. PARECER JURÍDICO Nº 5089/2022</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2015NE00581</t>
+          <t>2015NE00582</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35579.9</v>
+        <v>13845.87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -921,19 +921,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prestação de Serviço de Processamento de Dados. Especificação: Contratação de empresa especializada em Fornecimento de Circuito de Transmissão de Dados, compreendendo 02 (dois) links dedicados de 3 Mb</t>
+          <t>REFORÇO DA NE 00223- SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2015NE00582</t>
+          <t>2015NE00581</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13845.87</v>
+        <v>35579.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -951,14 +951,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 00223- SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO.</t>
+          <t>Prestação de Serviço de Processamento de Dados. Especificação: Contratação de empresa especializada em Fornecimento de Circuito de Transmissão de Dados, compreendendo 02 (dois) links dedicados de 3 Mb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023NE00297</t>
+          <t>2023NE0000297</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -981,14 +981,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2023 a 02/01/2024.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023NE0000297</t>
+          <t>2023NE00297</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1011,28 +1011,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2023 a 02/01/2024.</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021NE0000052</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1/2023</t>
-        </is>
-      </c>
+          <t>2021NE0000055</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>28/01/2021</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37800</v>
+        <v>25160</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1041,24 +1037,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 021, FINS AJUSTE DE DATA DA EMISSÃO</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 035, FINS AJUSTE DE DATA DA EMISSÃO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021NE0000055</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>2021NE0000052</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1/2023</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>28/01/2021</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25160</v>
+        <v>37800</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1067,17 +1067,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 035, FINS AJUSTE DE DATA DA EMISSÃO</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 021, FINS AJUSTE DE DATA DA EMISSÃO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2019NE00431</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>2019NE00430</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14/2017</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>27/05/2019</t>
@@ -1093,21 +1097,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DATA DE GERAÇÃO DO EMPENHO.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2019NE00430</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>14/2017</t>
-        </is>
-      </c>
+          <t>2019NE00431</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>27/05/2019</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DATA DE GERAÇÃO DO EMPENHO.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2015NE01104</t>
+          <t>2015NE01135</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1842.2</v>
+        <v>20754.94</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2015NE01135</t>
+          <t>2015NE01104</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20754.94</v>
+        <v>1842.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1504,10 +1504,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2019NE01976</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>2019NE01977</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>14/10/2019</t>
@@ -1523,21 +1527,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 1767 FINS AJUSTE Nº CONTRATO</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2019NE01977</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2019NE01976</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>14/10/2019</t>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
+          <t>ANULAÇÃO TOTAL DA NE 1767 FINS AJUSTE Nº CONTRATO</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2016NE00553</t>
+          <t>2016NE00535</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1613,28 +1613,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00142 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM, referen</t>
+          <t>Reconhecimento de dívida 2016RD00144 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM; referen</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2016NE00534</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>14/2012</t>
-        </is>
-      </c>
+          <t>2016NE00552</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>14/06/2016</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2964.99</v>
+        <v>17789.95</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1643,7 +1639,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00143 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM, referen</t>
+          <t>ANULAÇÃO TOTAL DA NE 00533 PARA CORREÇÃO NA DESCRIÇÃO DA NE.</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1676,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2016NE00552</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>2016NE00534</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>14/2012</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>14/06/2016</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17789.95</v>
+        <v>2964.99</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1699,14 +1699,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 00533 PARA CORREÇÃO NA DESCRIÇÃO DA NE.</t>
+          <t>Reconhecimento de dívida 2016RD00143 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM, referen</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2016NE00535</t>
+          <t>2016NE00553</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00144 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM; referen</t>
+          <t>Reconhecimento de dívida 2016RD00142 do 3º Aditivo ao Contrato nº 014/2012-PMAM - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A. - Contratação de Serviços de Telecomunicações para atender a PMAM, referen</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2015NE00732</t>
+          <t>2015NE00734</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>53369.85</v>
+        <v>13845.87</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1785,19 +1785,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>cobertura do 4º TA - MESES AGOSTO A OUT/2015</t>
+          <t>Serviço de processamento do sistema de controle de pessoal. 3° Termo Aditivo ao Contrato n° 002/12 Período de vigência: Início: 02/01/2015 Término: 02/01/2016 Contrato atende Decreto n° 35.616/2015</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2015NE00734</t>
+          <t>2015NE00732</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13845.87</v>
+        <v>53369.85</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Serviço de processamento do sistema de controle de pessoal. 3° Termo Aditivo ao Contrato n° 002/12 Período de vigência: Início: 02/01/2015 Término: 02/01/2016 Contrato atende Decreto n° 35.616/2015</t>
+          <t>cobertura do 4º TA - MESES AGOSTO A OUT/2015</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2021NE0000215</t>
+          <t>2021NE0000214</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9450</v>
+        <v>25160</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1875,19 +1875,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2021 a 02/01/2022.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2021NE0000214</t>
+          <t>2021NE0000215</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>25160</v>
+        <v>9450</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1905,19 +1905,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2021 a 02/01/2022.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2021NE0000678</t>
+          <t>2021NE0000683</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25160</v>
+        <v>37800</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1935,19 +1935,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021NE0000683</t>
+          <t>2021NE0000678</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>37800</v>
+        <v>25160</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento.</t>
         </is>
       </c>
     </row>
@@ -2002,10 +2002,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2018NE00929</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>2018NE00927</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14/2017</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>04/06/2018</t>
@@ -2021,7 +2025,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anulação total da NE 927, para correção na modalidade da NE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
@@ -2058,14 +2062,10 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018NE00927</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>14/2017</t>
-        </is>
-      </c>
+          <t>2018NE00929</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>04/06/2018</t>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>Anulação total da NE 927, para correção na modalidade da NE</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2021NE0000063</t>
+          <t>2021NE0000081</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>37800</v>
+        <v>25160</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2141,19 +2141,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2021 a 02/01/2022.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2021NE0000081</t>
+          <t>2021NE0000063</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25160</v>
+        <v>37800</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2171,19 +2171,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2021 a 02/01/2022.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2016NE00043</t>
+          <t>2016NE00042</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27691.74</v>
+        <v>106739.7</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2201,19 +2201,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada para a prestação de Serviços de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/11.</t>
+          <t>Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet com 6,9 MBPS e serviço de firewall - DOE 32.371,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2016NE00042</t>
+          <t>2016NE00043</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>106739.7</v>
+        <v>27691.74</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2231,14 +2231,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet com 6,9 MBPS e serviço de firewall - DOE 32.371,</t>
+          <t>Contratação de Empresa Especializada para a prestação de Serviços de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/11.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2015NE00721</t>
+          <t>2015NE00728</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>35579.9</v>
+        <v>17789.95</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados</t>
+          <t>Prestação de Serviço de Processamento de Dados. Especificação: Contratação de empresa especializada em Fornecimento de Circuito de Transmissão de Dados, compreendendo 02 (dois) links dedicados de 3 Mb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2015NE00728</t>
+          <t>2015NE00721</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17789.95</v>
+        <v>35579.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,14 +2321,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prestação de Serviço de Processamento de Dados. Especificação: Contratação de empresa especializada em Fornecimento de Circuito de Transmissão de Dados, compreendendo 02 (dois) links dedicados de 3 Mb</t>
+          <t>82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2015NE00649</t>
+          <t>2015NE00648</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: contratação de empresa especializada em prestação de serviços de desen</t>
+          <t>ANULAÇÃO PARCIAL DA NE 223 PARA CORREÇÃO DA REFERÊNCIA LEGAL E EMISSÃO DO NOVO EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2015NE00648</t>
+          <t>2015NE00649</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 223 PARA CORREÇÃO DA REFERÊNCIA LEGAL E EMISSÃO DO NOVO EMPENHO.</t>
+          <t>SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: contratação de empresa especializada em prestação de serviços de desen</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2016NE00444</t>
+          <t>2016NE00443</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2467,14 +2467,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00140,referente ao mês de Dezembro de 2015 - Contratação de empresa especializada em desenvolvimento de software ,NFS-e nº 17063 de 22/12/2015 (R$ 4.615,29).</t>
+          <t>Reconhecimento de dívida 2016RD00139 referente ao mês de Novembro de 2015 - Contratação de empresa especializada em desenvolvimento de software-NFS-e nº 16643 de 23/11/2015 (R$ 4.615,29).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2016NE00442</t>
+          <t>2016NE00441</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00138 referente ao mês de Dezembro de 2015 - Contratação de sv de telecomunicações da PRODAM NFS-e nº 16880 de 02/12/2015 (R$ 5.295,25), nº 16881 de 02/12/2015 (R$ 8.370</t>
+          <t>Reconhecimento de dívida 2016RD00137, mês de Novembro de 2015 -Contratação de serv. de telecomunicações da PRODAM - NFS-e nº 16533 de 10/11/2015 R$ 8.370,46), nº 16534 de 10/11/2015 (R$ 4.124,24) e nº</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2016NE00441</t>
+          <t>2016NE00442</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00137, mês de Novembro de 2015 -Contratação de serv. de telecomunicações da PRODAM - NFS-e nº 16533 de 10/11/2015 R$ 8.370,46), nº 16534 de 10/11/2015 (R$ 4.124,24) e nº</t>
+          <t>Reconhecimento de dívida 2016RD00138 referente ao mês de Dezembro de 2015 - Contratação de sv de telecomunicações da PRODAM NFS-e nº 16880 de 02/12/2015 (R$ 5.295,25), nº 16881 de 02/12/2015 (R$ 8.370</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2016NE00443</t>
+          <t>2016NE00444</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida 2016RD00139 referente ao mês de Novembro de 2015 - Contratação de empresa especializada em desenvolvimento de software-NFS-e nº 16643 de 23/11/2015 (R$ 4.615,29).</t>
+          <t>Reconhecimento de dívida 2016RD00140,referente ao mês de Dezembro de 2015 - Contratação de empresa especializada em desenvolvimento de software ,NFS-e nº 17063 de 22/12/2015 (R$ 4.615,29).</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
+          <t>2020NE00002</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>75480</v>
+        <v>47250</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2617,19 +2617,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2020 a 02/01/2021</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020NE00002</t>
+          <t>2020NE00003</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>47250</v>
+        <v>75480</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2647,19 +2647,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>Contratação de empresa especializada para implantação do sistema de Recursos Humanos e Folha de pagamento. Vigência: 12 (doze) meses, a contar de 02/01/2020 a 02/01/2021</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019NE00001</t>
+          <t>2019NE00006</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>18870</v>
+        <v>28350</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2677,19 +2677,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2019NE00006</t>
+          <t>2019NE00001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28350</v>
+        <v>18870</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2707,24 +2707,28 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2018NE00059</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>2018NE00069</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>47250</v>
+        <v>75480</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2733,14 +2737,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE PARA CORREÇÃO DA DESCRIÇÃO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA (PRODAM) NA PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL (CPPM), FINS ATENDER AS NECESSIDADES DA PMAM</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2018NE00053</t>
+          <t>2018NE00065</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2770,7 +2774,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018NE00065</t>
+          <t>2018NE00053</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2800,21 +2804,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018NE00069</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2018NE00059</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>75480</v>
+        <v>47250</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA (PRODAM) NA PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL (CPPM), FINS ATENDER AS NECESSIDADES DA PMAM</t>
+          <t>ANULAÇÃO TOTAL DA NE PARA CORREÇÃO DA DESCRIÇÃO</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2860,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2014NE00050</t>
+          <t>2014NE00035</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>152069.75</v>
+        <v>53430.96</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2883,19 +2883,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Contrato No. 14/2012 - Link 3 Mpbs, Internet 4,4 Mpbs, Firewall</t>
+          <t>Contrato No. 2/2012 - CPPM - Cadastro de Pessoal da Polícia Militar</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2014NE00035</t>
+          <t>2014NE00050</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>53430.96</v>
+        <v>152069.75</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2913,28 +2913,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2012 - CPPM - Cadastro de Pessoal da Polícia Militar</t>
+          <t>Contrato No. 14/2012 - Link 3 Mpbs, Internet 4,4 Mpbs, Firewall</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2017NE02102</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2/2012</t>
-        </is>
-      </c>
+          <t>2017NE02101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4615.29</v>
+        <v>9450</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2943,24 +2939,28 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2017NE02101</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>2017NE02102</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2/2012</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>9450</v>
+        <v>4615.29</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2969,19 +2969,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2017NE01737</t>
+          <t>2017NE01732</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4615.29</v>
+        <v>9450</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2999,19 +2999,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2017NE01732</t>
+          <t>2017NE01737</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9450</v>
+        <v>4615.29</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3029,19 +3029,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2019NE01767</t>
+          <t>2019NE01768</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>18870</v>
+        <v>28350</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3059,19 +3059,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2019NE01768</t>
+          <t>2019NE01767</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>28350</v>
+        <v>18870</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2017NE01216</t>
+          <t>2017NE01224</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9230.58</v>
+        <v>18900</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3115,14 +3115,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2017NE01224</t>
+          <t>2017NE01216</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>18900</v>
+        <v>9230.58</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>Contratação de Empresa Especializada para prestação de serviço de Cadastro de pessoas da PMAM - Disp. Lic. DOE 32.223 de 28/12/2011.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019NE01126</t>
+          <t>2019NE01127</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>28350</v>
+        <v>18870</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3167,14 +3167,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2019NE01127</t>
+          <t>2019NE01126</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>18870</v>
+        <v>28350</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
+          <t>Contratação de empresa para prestação, de forma dedicada, de serviço de acesso á internet por fibra óptica com garantia de 100(por cento) em download e upload, inclusos equipamentos e instalação, conf</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2016NE00468</t>
+          <t>2016NE00467</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13845.87</v>
+        <v>17789.95</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3253,19 +3253,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 0043/2016 SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: contratação de empresa especializada em prestação de serviços de desenvolvimento de software aplicativo para co</t>
+          <t>REFORÇO NE 0042/2016 82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibiliz</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2016NE00467</t>
+          <t>2016NE00468</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17789.95</v>
+        <v>13845.87</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3283,19 +3283,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>REFORÇO NE 0042/2016 82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibiliz</t>
+          <t>REFORÇO DA NE 0043/2016 SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE DE APLICAÇÃO, Descrição: contratação de empresa especializada em prestação de serviços de desenvolvimento de software aplicativo para co</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2019NE00161</t>
+          <t>2019NE00159</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>14/2017</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>18870</v>
+        <v>18900</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3313,19 +3313,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2019NE00159</t>
+          <t>2019NE00161</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>18900</v>
+        <v>18870</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3343,19 +3343,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada para a prestação de serviço de informática, no Fornecimento de Circuito de Transmissão de Dados, acesso a Internet dedicado com velocidade de 15 Mbps. Portaria nº </t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CONTROLE DE PESSOAL - CPPM, FISN ATENDER AS NECESSIDADES DA PMAM.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2015NE00415</t>
+          <t>2015NE00414</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>23079.85</v>
+        <v>4615.29</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3373,19 +3373,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 00027 REFERENTE CONTRATO 014/2012-PMAM</t>
+          <t>REFORÇO DA NE 00223 REFERENTE CONTRATO 002/2012-PMAM</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2015NE00414</t>
+          <t>2015NE00415</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>14/2012</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4615.29</v>
+        <v>23079.85</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 00223 REFERENTE CONTRATO 002/2012-PMAM</t>
+          <t>REFORÇO DA NE 00027 REFERENTE CONTRATO 014/2012-PMAM</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/PMAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/PMAM/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-12-31</t>
         </is>
       </c>
     </row>
